--- a/csv/policies/reference/Ref_CER/formula_Ref_CER_ON.xlsx
+++ b/csv/policies/reference/Ref_CER/formula_Ref_CER_ON.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
